--- a/shared/aportes_tanque_manuales.xlsx
+++ b/shared/aportes_tanque_manuales.xlsx
@@ -2,15 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-26520" yWindow="615" windowWidth="14610" windowHeight="15585" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="aportes_tanque_manuales" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -26,6 +25,7 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="FF1F6F4A"/>
       <sz val="9"/>
@@ -56,17 +56,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -429,87 +431,84 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:L16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="34" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="44" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" style="3" min="1" max="2"/>
+    <col width="9" customWidth="1" style="3" min="3" max="3"/>
+    <col width="10" customWidth="1" style="3" min="4" max="5"/>
+    <col width="13" customWidth="1" style="3" min="6" max="6"/>
+    <col width="11" customWidth="1" style="3" min="7" max="7"/>
+    <col width="10" customWidth="1" style="3" min="8" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="15" customWidth="1" style="3" min="11" max="11"/>
+    <col width="44" customWidth="1" style="3" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="42" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="42" customHeight="1" s="3">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Aportes al tanque comunitario que llegaron mal ubicados o desfasados y se corrigen a mano. Writer unico humano, no lo escribe ningun main.py. Precursor de caja.MovimientoCaja BALDE=tanque (reasignado). consolidar_tanque.py lo lee como fuente durable.</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="20" customHeight="1" s="3">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>MZ</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>LT</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>MONTO</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>BALDE</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>CANAL</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>FECHA_REAL</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>MES_CICLO</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>MZ_ORIGEN</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>LT_ORIGEN</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>EVIDENCIA</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K2" s="1" t="inlineStr">
         <is>
           <t>MES_ANO_APLICA</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L2" s="1" t="inlineStr">
         <is>
           <t>MOTIVO</t>
         </is>
@@ -944,6 +943,342 @@
       <c r="L10" t="inlineStr">
         <is>
           <t>Aporte tanque de H1-3 confirmado por la secretaria (25/07/2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>50</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>tanque</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>yape</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>pagos_yape_tepago.xlsx (archivo 2026-07) / ReporteTransacciones+51948227636.xlsx. Irma Huanahui Lopez (U0045), dos yapes el mismo minuto 07/07 10:15-10:23: S/58 mensaje 'm.z.c.lt.13' (matcheo bien) y S/15 mensaje 'mz.lt11' (sin letra de manzana, cayo por default de maestro a C-13 -- ver reidentificacion.xlsx). C-13 solo debia 8 de agua; el excedente de la primera transaccion (58-8=50) es aporte tanque, confirmado por la secretaria (cuaderno papel, Reclamos agosto). El otro balde (S/15, la porcion mal atribuida) va en reidentificacion.xlsx, mismo ancla.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Aporte tanque de C-13 (Irma Huanahui) identificado al investigar el reclamo de K-11 (Martina Morales) -- ver reclamos_manuales.xlsx fila K-11 y reidentificacion.xlsx C-13-&gt;K-11.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>400</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>tanque</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>yape</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>22/07/2026</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>pagos_yape_tepago_2026-08.xlsx, USER_ID Aubertina Trujillo Tolentino. Mensaje: 'mz k Lt 2,mz C1 Lt 2 tanque' (22/07/2026 17:22:52). Deuda real 8 (5 agua+3 mant), ya cubierta por otro yape de S/8 el 02/08 ('MZ.C1 LT.2'). El S/400 con 'tanque' explicito en el mensaje es 100% tanque, sin resto -- coincide exacto con el exceso registrado (-400) en arrastre_devolucion_2026-08.xlsx.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Aporte tanque de C1-2 detectado al revisar excesos de arrastre_devolucion_2026-08.xlsx buscando CONCEPTO=tanque sin marcar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>36</v>
+      </c>
+      <c r="C13" t="n">
+        <v>50</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>tanque</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>yape</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>46235</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Aporte que vino del exeso de agosto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>100</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>tanque</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>yape</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>26/07/2026</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>pagos_yape_tepago_2026-08.xlsx, Leonardo Huamani Sotelo. Janet Vil* mando 5 yapes seguidos el 26/07 17:32-17:37 (100,150,200,200,200), los otros 4 dicen 'tanque' explicito y ya estan en aportes_tanque_manuales -- este (100, 'mz V lt 14', 17:32:34) es el primero de la tanda, se le olvido escribir 'tanque' pero es el mismo patron/misma persona/mismos minutos.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Aporte tanque de V-14 detectado al revisar excesos de arrastre_devolucion_2026-08.xlsx -- sin este, V-14 parece EXCESO(-67) cuando en realidad sigue debiendo 33 (incluye MULTA 20 sin pagar de verdad).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>200</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>tanque</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>yape</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>23/07/2026</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>pagos_yape_tepago_2026-08.xlsx, Julio Solorzano Estrada. Yape S/200 el 23/07/2026 19:33:40, mensaje 'I 13 Julio Solorzano Estrada' (sin la palabra tanque). Deuda real 21 (18 agua+3 mant), ya cubierta por otro yape de S/21 el 04/08. El S/200 es 100% tanque, sin resto -- coincide exacto con el exceso registrado (-200) en arrastre_devolucion_2026-08.xlsx.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Aporte tanque de I-13 confirmado (referido por el usuario) al revisar excesos de arrastre_devolucion_2026-08.xlsx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>50</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>tanque</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>yape</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>pagos_yape_tepago_2026-08.xlsx, Tito Cosme Castillejo. Yape S/50 el 24/07/2026 19:35:44, mensaje 'Nancy Montalvo cano Mz.H1 Lt.36' (sin la palabra tanque; distinto del otro yape de H1-36, S/50 el 01/08, que si dice tanque y ya estaba cargado). Confirmado por el usuario que este tambien es tanque.</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Aporte tanque de H1-36 (segundo deposito, 24/07) confirmado (referido por el usuario) al revisar excesos de arrastre_devolucion_2026-08.xlsx.</t>
         </is>
       </c>
     </row>
